--- a/結合テスト/結合結果/会員結合結果.xlsx
+++ b/結合テスト/結合結果/会員結合結果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shogo.maeda\Downloads\workspace\Bacon-2\結合テスト\結合結果\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCD0C442-F3AE-4328-BABF-1BC40A968C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DA91BE6-9B92-40A1-942D-6D0C6502B4FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C0160774-731D-410A-8BA8-13CF71C62EE1}"/>
   </bookViews>
